--- a/文档资料/随从数据表.xlsx
+++ b/文档资料/随从数据表.xlsx
@@ -16,6 +16,9 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$29</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="74">
   <si>
     <t>ID</t>
   </si>
@@ -132,7 +135,7 @@
     <t>战斗结束获得一个该品质【苹果】</t>
   </si>
   <si>
-    <t>亏摸，带收益</t>
+    <t>亏模，带收益</t>
   </si>
   <si>
     <t>猎人</t>
@@ -141,13 +144,121 @@
     <t>射手</t>
   </si>
   <si>
+    <t>攻击【荒辽】随从时暴击率+10%</t>
+  </si>
+  <si>
+    <t>白模射手，一定特点</t>
+  </si>
+  <si>
+    <t>攻击【荒辽】随从时暴击率+20%</t>
+  </si>
+  <si>
+    <t>攻击【荒辽】随从时暴击率+30%</t>
+  </si>
+  <si>
     <t>攻击【荒辽】随从时暴击率+50%</t>
   </si>
   <si>
-    <t>白模射手，一定特点</t>
-  </si>
-  <si>
-    <t>攻击【荒辽】随从时暴击率+100%</t>
+    <t>拳师</t>
+  </si>
+  <si>
+    <t>频率随从</t>
+  </si>
+  <si>
+    <t>弓箭手</t>
+  </si>
+  <si>
+    <t>造成120%伤害</t>
+  </si>
+  <si>
+    <t>亏模，高成长</t>
+  </si>
+  <si>
+    <t>造成130%伤害</t>
+  </si>
+  <si>
+    <t>造成140%伤害</t>
+  </si>
+  <si>
+    <t>造成150%伤害</t>
+  </si>
+  <si>
+    <t>屠夫</t>
+  </si>
+  <si>
+    <t>敌方随从死亡时，回复100%攻击的生命，自己造成击杀时额外回复100%攻击的生命</t>
+  </si>
+  <si>
+    <t>敌方随从死亡时，回复100%攻击的生命，自己造成击杀时额外回复150%攻击的生命</t>
+  </si>
+  <si>
+    <t>敌方随从死亡时，回复100%攻击的生命，自己造成击杀时额外回复200%攻击的生命</t>
+  </si>
+  <si>
+    <t>敌方随从死亡时，回复100%攻击的生命，自己造成击杀时额外回复300%攻击的生命</t>
+  </si>
+  <si>
+    <t>浪客</t>
+  </si>
+  <si>
+    <t>刺客</t>
+  </si>
+  <si>
+    <t>对血量低于30%的敌人造成120%伤害</t>
+  </si>
+  <si>
+    <t>斩杀线高</t>
+  </si>
+  <si>
+    <t>对血量低于30%的敌人造成150%伤害</t>
+  </si>
+  <si>
+    <t>对血量低于50%的敌人造成150%伤害</t>
+  </si>
+  <si>
+    <t>对血量低于50%的敌人造成200%伤害</t>
+  </si>
+  <si>
+    <t>铁匠</t>
+  </si>
+  <si>
+    <t>辅助</t>
+  </si>
+  <si>
+    <t>提升身后友军10点攻击力</t>
+  </si>
+  <si>
+    <t>局内增益辅助</t>
+  </si>
+  <si>
+    <t>提升身后友军20点攻击力</t>
+  </si>
+  <si>
+    <t>提升身后友军40点攻击力</t>
+  </si>
+  <si>
+    <t>提升身后友军80点攻击力</t>
+  </si>
+  <si>
+    <t>织女</t>
+  </si>
+  <si>
+    <t>为1名随机友方提供100%攻击力的护盾</t>
+  </si>
+  <si>
+    <t>加盾的</t>
+  </si>
+  <si>
+    <t>为2名随机友方提供100%攻击力的护盾</t>
+  </si>
+  <si>
+    <t>加盾的，感觉是个轮椅</t>
+  </si>
+  <si>
+    <t>为3名随机友方提供100%攻击力的护盾</t>
+  </si>
+  <si>
+    <t>为4名随机友方提供100%攻击力的护盾</t>
   </si>
 </sst>
 </file>
@@ -786,7 +897,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -794,9 +905,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1113,7 +1221,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="7.89090909090909" style="2" customWidth="1"/>
@@ -1127,56 +1235,56 @@
     <col min="12" max="12" width="7.78181818181818" style="2" customWidth="1"/>
     <col min="13" max="13" width="7.49090909090909" style="2" customWidth="1"/>
     <col min="14" max="14" width="8.66363636363636" style="2" customWidth="1"/>
-    <col min="15" max="15" width="19.0909090909091" style="2" customWidth="1"/>
-    <col min="16" max="16" width="31.5363636363636" style="2" customWidth="1"/>
+    <col min="15" max="15" width="38.2454545454545" style="2" customWidth="1"/>
+    <col min="16" max="16" width="51.5363636363636" style="2" customWidth="1"/>
     <col min="17" max="17" width="24.8272727272727" style="2" customWidth="1"/>
     <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -1418,7 +1526,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H6" s="2">
         <v>10</v>
@@ -1467,9 +1575,8 @@
       <c r="E7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="2"/>
       <c r="G7" s="2">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H7" s="2">
         <v>10</v>
@@ -1518,9 +1625,8 @@
       <c r="E8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="2"/>
       <c r="G8" s="2">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="H8" s="2">
         <v>10</v>
@@ -1570,7 +1676,7 @@
         <v>28</v>
       </c>
       <c r="G9" s="2">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="H9" s="2">
         <v>10</v>
@@ -1653,7 +1759,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" customHeight="1" spans="1:17">
       <c r="A11" s="2">
         <v>10032</v>
       </c>
@@ -1835,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M14" s="2">
         <v>100</v>
@@ -1885,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M15" s="2">
         <v>100</v>
@@ -1897,7 +2003,7 @@
         <v>21</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>36</v>
@@ -1926,7 +2032,7 @@
         <v>30</v>
       </c>
       <c r="I16" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J16" s="2">
         <v>0</v>
@@ -1935,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M16" s="2">
         <v>100</v>
@@ -1947,7 +2053,7 @@
         <v>21</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>36</v>
@@ -1976,7 +2082,7 @@
         <v>50</v>
       </c>
       <c r="I17" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" s="2">
         <v>0</v>
@@ -1985,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M17" s="2">
         <v>100</v>
@@ -1997,13 +2103,1204 @@
         <v>21</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>36</v>
       </c>
     </row>
+    <row r="18" spans="1:17">
+      <c r="A18" s="2">
+        <v>10051</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="2">
+        <v>80</v>
+      </c>
+      <c r="H18" s="2">
+        <v>10</v>
+      </c>
+      <c r="I18" s="2">
+        <v>3</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
+        <v>80</v>
+      </c>
+      <c r="N18" s="2">
+        <v>20</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="2">
+        <v>10052</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="2">
+        <v>100</v>
+      </c>
+      <c r="H19" s="2">
+        <v>10</v>
+      </c>
+      <c r="I19" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2">
+        <v>80</v>
+      </c>
+      <c r="N19" s="2">
+        <v>20</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="2">
+        <v>10053</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="2">
+        <v>120</v>
+      </c>
+      <c r="H20" s="2">
+        <v>10</v>
+      </c>
+      <c r="I20" s="2">
+        <v>2</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2">
+        <v>80</v>
+      </c>
+      <c r="N20" s="2">
+        <v>20</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" s="2">
+        <v>10054</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="2">
+        <v>150</v>
+      </c>
+      <c r="H21" s="2">
+        <v>10</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2">
+        <v>80</v>
+      </c>
+      <c r="N21" s="2">
+        <v>20</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22" s="2">
+        <v>10061</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="2">
+        <v>50</v>
+      </c>
+      <c r="H22" s="2">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2">
+        <v>5</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>120</v>
+      </c>
+      <c r="N22" s="2">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" s="2">
+        <v>10062</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="2">
+        <v>50</v>
+      </c>
+      <c r="H23" s="2">
+        <v>40</v>
+      </c>
+      <c r="I23" s="2">
+        <v>5</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0</v>
+      </c>
+      <c r="K23" s="2">
+        <v>0</v>
+      </c>
+      <c r="L23" s="2">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2">
+        <v>130</v>
+      </c>
+      <c r="N23" s="2">
+        <v>0</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" s="2">
+        <v>10063</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="2">
+        <v>50</v>
+      </c>
+      <c r="H24" s="2">
+        <v>50</v>
+      </c>
+      <c r="I24" s="2">
+        <v>5</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2">
+        <v>140</v>
+      </c>
+      <c r="N24" s="2">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="2">
+        <v>10064</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="2">
+        <v>50</v>
+      </c>
+      <c r="H25" s="2">
+        <v>80</v>
+      </c>
+      <c r="I25" s="2">
+        <v>5</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2">
+        <v>150</v>
+      </c>
+      <c r="N25" s="2">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="2">
+        <v>10071</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="2">
+        <v>150</v>
+      </c>
+      <c r="H26" s="2">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2">
+        <v>10</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2">
+        <v>100</v>
+      </c>
+      <c r="N26" s="2">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="2">
+        <v>10072</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" s="2">
+        <v>300</v>
+      </c>
+      <c r="H27" s="2">
+        <v>40</v>
+      </c>
+      <c r="I27" s="2">
+        <v>10</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2">
+        <v>100</v>
+      </c>
+      <c r="N27" s="2">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" s="2">
+        <v>10073</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="2">
+        <v>450</v>
+      </c>
+      <c r="H28" s="2">
+        <v>50</v>
+      </c>
+      <c r="I28" s="2">
+        <v>10</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2">
+        <v>100</v>
+      </c>
+      <c r="N28" s="2">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29" s="2">
+        <v>10074</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" s="2">
+        <v>600</v>
+      </c>
+      <c r="H29" s="2">
+        <v>50</v>
+      </c>
+      <c r="I29" s="2">
+        <v>10</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2">
+        <v>100</v>
+      </c>
+      <c r="N29" s="2">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30" s="2">
+        <v>10081</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30" s="2">
+        <v>60</v>
+      </c>
+      <c r="H30" s="2">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2">
+        <v>6</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2">
+        <v>100</v>
+      </c>
+      <c r="N30" s="2">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31" s="2">
+        <v>10082</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" s="2">
+        <v>60</v>
+      </c>
+      <c r="H31" s="2">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2">
+        <v>6</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2">
+        <v>100</v>
+      </c>
+      <c r="N31" s="2">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
+      <c r="A32" s="2">
+        <v>10083</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32" s="2">
+        <v>60</v>
+      </c>
+      <c r="H32" s="2">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2">
+        <v>6</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2">
+        <v>100</v>
+      </c>
+      <c r="N32" s="2">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" s="2">
+        <v>10084</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" s="2">
+        <v>60</v>
+      </c>
+      <c r="H33" s="2">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2">
+        <v>6</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0</v>
+      </c>
+      <c r="K33" s="2">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2">
+        <v>100</v>
+      </c>
+      <c r="N33" s="2">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" s="2">
+        <v>10091</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34" s="2">
+        <v>120</v>
+      </c>
+      <c r="H34" s="2">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2">
+        <v>8</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2">
+        <v>100</v>
+      </c>
+      <c r="N34" s="2">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35" s="2">
+        <v>10092</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G35" s="2">
+        <v>150</v>
+      </c>
+      <c r="H35" s="2">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2">
+        <v>8</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0</v>
+      </c>
+      <c r="K35" s="2">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2">
+        <v>100</v>
+      </c>
+      <c r="N35" s="2">
+        <v>0</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" s="2">
+        <v>10093</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G36" s="2">
+        <v>180</v>
+      </c>
+      <c r="H36" s="2">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2">
+        <v>8</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2">
+        <v>100</v>
+      </c>
+      <c r="N36" s="2">
+        <v>0</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" s="2">
+        <v>10094</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37" s="2">
+        <v>210</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2">
+        <v>8</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0</v>
+      </c>
+      <c r="K37" s="2">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2">
+        <v>100</v>
+      </c>
+      <c r="N37" s="2">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" s="2">
+        <v>10101</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38" s="2">
+        <v>40</v>
+      </c>
+      <c r="H38" s="2">
+        <v>10</v>
+      </c>
+      <c r="I38" s="2">
+        <v>10</v>
+      </c>
+      <c r="J38" s="2">
+        <v>0</v>
+      </c>
+      <c r="K38" s="2">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2">
+        <v>100</v>
+      </c>
+      <c r="N38" s="2">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="A39" s="2">
+        <v>10102</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G39" s="2">
+        <v>40</v>
+      </c>
+      <c r="H39" s="2">
+        <v>10</v>
+      </c>
+      <c r="I39" s="2">
+        <v>10</v>
+      </c>
+      <c r="J39" s="2">
+        <v>0</v>
+      </c>
+      <c r="K39" s="2">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2">
+        <v>100</v>
+      </c>
+      <c r="N39" s="2">
+        <v>0</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40" s="2">
+        <v>10103</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G40" s="2">
+        <v>40</v>
+      </c>
+      <c r="H40" s="2">
+        <v>10</v>
+      </c>
+      <c r="I40" s="2">
+        <v>10</v>
+      </c>
+      <c r="J40" s="2">
+        <v>0</v>
+      </c>
+      <c r="K40" s="2">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2">
+        <v>100</v>
+      </c>
+      <c r="N40" s="2">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" s="2">
+        <v>10104</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G41" s="2">
+        <v>40</v>
+      </c>
+      <c r="H41" s="2">
+        <v>10</v>
+      </c>
+      <c r="I41" s="2">
+        <v>10</v>
+      </c>
+      <c r="J41" s="2">
+        <v>0</v>
+      </c>
+      <c r="K41" s="2">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2">
+        <v>0</v>
+      </c>
+      <c r="M41" s="2">
+        <v>100</v>
+      </c>
+      <c r="N41" s="2">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Q29" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/文档资料/随从数据表.xlsx
+++ b/文档资料/随从数据表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$S$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="80">
   <si>
     <t>ID</t>
   </si>
@@ -84,9 +84,15 @@
     <t>skill</t>
   </si>
   <si>
+    <t>target</t>
+  </si>
+  <si>
     <t>character</t>
   </si>
   <si>
+    <t>photo</t>
+  </si>
+  <si>
     <t>description</t>
   </si>
   <si>
@@ -105,9 +111,15 @@
     <t>造成100%伤害</t>
   </si>
   <si>
+    <t>最近</t>
+  </si>
+  <si>
     <t>无</t>
   </si>
   <si>
+    <t>Assets/Resources/Follower/test.jpg</t>
+  </si>
+  <si>
     <t>最普通的士兵，数值标准。</t>
   </si>
   <si>
@@ -144,6 +156,9 @@
     <t>射手</t>
   </si>
   <si>
+    <t>直线</t>
+  </si>
+  <si>
     <t>攻击【荒辽】随从时暴击率+10%</t>
   </si>
   <si>
@@ -244,6 +259,9 @@
   </si>
   <si>
     <t>为1名随机友方提供100%攻击力的护盾</t>
+  </si>
+  <si>
+    <t>随机</t>
   </si>
   <si>
     <t>加盾的</t>
@@ -1221,27 +1239,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:S42"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.89090909090909" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.2636363636364" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.2090909090909" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14.1272727272727" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.59090909090909" style="2" customWidth="1"/>
-    <col min="6" max="6" width="8.80909090909091" style="2" customWidth="1"/>
+    <col min="1" max="1" width="7.88888888888889" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.2592592592593" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.212962962963" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.1296296296296" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.59259259259259" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8.80555555555556" style="2" customWidth="1"/>
     <col min="7" max="10" width="9" style="2"/>
-    <col min="11" max="11" width="10.9727272727273" style="2" customWidth="1"/>
-    <col min="12" max="12" width="7.78181818181818" style="2" customWidth="1"/>
-    <col min="13" max="13" width="7.49090909090909" style="2" customWidth="1"/>
-    <col min="14" max="14" width="8.66363636363636" style="2" customWidth="1"/>
-    <col min="15" max="15" width="38.2454545454545" style="2" customWidth="1"/>
-    <col min="16" max="16" width="51.5363636363636" style="2" customWidth="1"/>
-    <col min="17" max="17" width="24.8272727272727" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="2"/>
+    <col min="11" max="11" width="10.9722222222222" style="2" customWidth="1"/>
+    <col min="12" max="12" width="7.77777777777778" style="2" customWidth="1"/>
+    <col min="13" max="13" width="7.49074074074074" style="2" customWidth="1"/>
+    <col min="14" max="14" width="8.66666666666667" style="2" customWidth="1"/>
+    <col min="15" max="15" width="38.25" style="2" customWidth="1"/>
+    <col min="16" max="16" width="10.25" style="2" customWidth="1"/>
+    <col min="17" max="17" width="51.537037037037" style="2" customWidth="1"/>
+    <col min="18" max="18" width="44.1759259259259" style="2" customWidth="1"/>
+    <col min="19" max="19" width="24.8240740740741" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:17">
+    <row r="1" s="1" customFormat="1" ht="24" customHeight="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1293,22 +1313,28 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="2">
         <v>10011</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
@@ -1338,30 +1364,36 @@
         <v>0</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" s="2">
         <v>10012</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
@@ -1391,30 +1423,36 @@
         <v>0</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4" s="2">
         <v>10013</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
@@ -1444,30 +1482,36 @@
         <v>0</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" s="2">
         <v>10014</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
@@ -1497,30 +1541,36 @@
         <v>0</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" s="2">
         <v>10021</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
@@ -1550,30 +1600,39 @@
         <v>0</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" s="2">
         <v>10022</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
       </c>
       <c r="G7" s="2">
         <v>500</v>
@@ -1600,30 +1659,39 @@
         <v>0</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" s="2">
         <v>10023</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
       </c>
       <c r="G8" s="2">
         <v>800</v>
@@ -1650,30 +1718,39 @@
         <v>0</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" s="2">
         <v>10024</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
       </c>
       <c r="G9" s="2">
         <v>1200</v>
@@ -1700,30 +1777,39 @@
         <v>0</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" s="2">
         <v>10031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
       </c>
       <c r="G10" s="2">
         <v>80</v>
@@ -1750,30 +1836,39 @@
         <v>0</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:17">
+        <v>35</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" ht="14" customHeight="1" spans="1:19">
       <c r="A11" s="2">
         <v>10032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
       </c>
       <c r="G11" s="2">
         <v>120</v>
@@ -1800,30 +1895,39 @@
         <v>0</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
+        <v>35</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" s="2">
         <v>10033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
       </c>
       <c r="G12" s="2">
         <v>160</v>
@@ -1850,30 +1954,39 @@
         <v>0</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17">
+        <v>35</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" s="2">
         <v>10034</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
       </c>
       <c r="G13" s="2">
         <v>200</v>
@@ -1900,30 +2013,39 @@
         <v>0</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17">
+        <v>35</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" s="2">
         <v>10041</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
       </c>
       <c r="G14" s="2">
         <v>75</v>
@@ -1950,30 +2072,39 @@
         <v>0</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17">
+        <v>40</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" s="2">
         <v>10042</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
       </c>
       <c r="G15" s="2">
         <v>75</v>
@@ -2000,30 +2131,39 @@
         <v>0</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
+        <v>42</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" s="2">
         <v>10043</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
       </c>
       <c r="G16" s="2">
         <v>75</v>
@@ -2050,30 +2190,39 @@
         <v>0</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
+        <v>43</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="2">
         <v>10044</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
       </c>
       <c r="G17" s="2">
         <v>75</v>
@@ -2100,30 +2249,39 @@
         <v>0</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>39</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
+        <v>44</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="2">
         <v>10051</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
       </c>
       <c r="G18" s="2">
         <v>80</v>
@@ -2150,30 +2308,39 @@
         <v>20</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" s="2">
         <v>10052</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
       </c>
       <c r="G19" s="2">
         <v>100</v>
@@ -2200,30 +2367,39 @@
         <v>20</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" s="2">
         <v>10053</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
       </c>
       <c r="G20" s="2">
         <v>120</v>
@@ -2250,30 +2426,39 @@
         <v>20</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" s="2">
         <v>10054</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
       </c>
       <c r="G21" s="2">
         <v>150</v>
@@ -2300,30 +2485,39 @@
         <v>20</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" s="2">
         <v>10061</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
       </c>
       <c r="G22" s="2">
         <v>50</v>
@@ -2350,30 +2544,39 @@
         <v>0</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" s="2">
         <v>10062</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
       </c>
       <c r="G23" s="2">
         <v>50</v>
@@ -2400,30 +2603,39 @@
         <v>0</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
       <c r="A24" s="2">
         <v>10063</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
       </c>
       <c r="G24" s="2">
         <v>50</v>
@@ -2450,30 +2662,39 @@
         <v>0</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" s="2">
         <v>10064</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
       </c>
       <c r="G25" s="2">
         <v>50</v>
@@ -2500,30 +2721,39 @@
         <v>0</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" s="2">
         <v>10071</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
       </c>
       <c r="G26" s="2">
         <v>150</v>
@@ -2550,27 +2780,36 @@
         <v>0</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17">
+        <v>24</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
       <c r="A27" s="2">
         <v>10072</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1</v>
       </c>
       <c r="G27" s="2">
         <v>300</v>
@@ -2597,27 +2836,36 @@
         <v>0</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17">
+        <v>24</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" s="2">
         <v>10073</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
       </c>
       <c r="G28" s="2">
         <v>450</v>
@@ -2644,27 +2892,36 @@
         <v>0</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17">
+        <v>24</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" s="2">
         <v>10074</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1</v>
       </c>
       <c r="G29" s="2">
         <v>600</v>
@@ -2691,27 +2948,36 @@
         <v>0</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17">
+        <v>24</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" s="2">
         <v>10081</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1</v>
       </c>
       <c r="G30" s="2">
         <v>60</v>
@@ -2738,30 +3004,39 @@
         <v>0</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17">
+        <v>60</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" s="2">
         <v>10082</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1</v>
       </c>
       <c r="G31" s="2">
         <v>60</v>
@@ -2788,30 +3063,39 @@
         <v>0</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17">
+        <v>62</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" s="2">
         <v>10083</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1</v>
       </c>
       <c r="G32" s="2">
         <v>60</v>
@@ -2838,30 +3122,39 @@
         <v>0</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17">
+        <v>63</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33" s="2">
         <v>10084</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
+      </c>
+      <c r="F33" s="2">
+        <v>1</v>
       </c>
       <c r="G33" s="2">
         <v>60</v>
@@ -2888,30 +3181,39 @@
         <v>0</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17">
+        <v>64</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34" s="2">
         <v>10091</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1</v>
       </c>
       <c r="G34" s="2">
         <v>120</v>
@@ -2938,30 +3240,39 @@
         <v>0</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
       <c r="A35" s="2">
         <v>10092</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
+      </c>
+      <c r="F35" s="2">
+        <v>1</v>
       </c>
       <c r="G35" s="2">
         <v>150</v>
@@ -2988,30 +3299,39 @@
         <v>0</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
       <c r="A36" s="2">
         <v>10093</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
+      </c>
+      <c r="F36" s="2">
+        <v>1</v>
       </c>
       <c r="G36" s="2">
         <v>180</v>
@@ -3038,30 +3358,39 @@
         <v>0</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S36" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
       <c r="A37" s="2">
         <v>10094</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
+      </c>
+      <c r="F37" s="2">
+        <v>1</v>
       </c>
       <c r="G37" s="2">
         <v>210</v>
@@ -3088,30 +3417,39 @@
         <v>0</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
       <c r="A38" s="2">
         <v>10101</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
+      </c>
+      <c r="F38" s="2">
+        <v>1</v>
       </c>
       <c r="G38" s="2">
         <v>40</v>
@@ -3138,30 +3476,39 @@
         <v>0</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
       <c r="A39" s="2">
         <v>10102</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
       </c>
       <c r="G39" s="2">
         <v>40</v>
@@ -3188,30 +3535,39 @@
         <v>0</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19">
       <c r="A40" s="2">
         <v>10103</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1</v>
       </c>
       <c r="G40" s="2">
         <v>40</v>
@@ -3238,30 +3594,39 @@
         <v>0</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19">
       <c r="A41" s="2">
         <v>10104</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1</v>
       </c>
       <c r="G41" s="2">
         <v>40</v>
@@ -3288,17 +3653,28 @@
         <v>0</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>71</v>
+        <v>25</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S41" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19">
+      <c r="R42" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Q29" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:S41" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3311,7 +3687,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3323,7 +3699,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
